--- a/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
@@ -399,7 +399,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="4">
@@ -431,7 +431,7 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>81</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="5">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C8">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>15.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>84.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="5">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C8">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>23.9</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Haryana/results/SoIB_summaries.xlsx
@@ -396,10 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -428,10 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>77.3</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="5">
@@ -444,10 +444,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -460,10 +460,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C8">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2">
-        <v>68</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>76.09999999999999</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>31.1</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>23.9</v>
+        <v>26.8</v>
       </c>
     </row>
   </sheetData>
